--- a/data/config/luban/config/general/task.xlsx
+++ b/data/config/luban/config/general/task.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="17100" windowHeight="7005"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1244,8 +1244,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
@@ -1255,7 +1255,7 @@
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1303,26 +1303,239 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:6">
+    <row r="4" s="2" customFormat="1" spans="1:7">
       <c r="B4" s="2">
-        <f>(C4+1)*1000000+D4*10000+E4</f>
-        <v>1010000</v>
+        <f t="shared" ref="B4:B13" si="0">(C4+1)*1000000+D4*1000+G4</f>
+        <v>3003001</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>100001</v>
       </c>
       <c r="F4" s="2">
         <v>100</v>
       </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5" s="2">
+        <f t="shared" si="0"/>
+        <v>3003002</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F5" s="2">
+        <v>200</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6" s="2">
+        <f t="shared" si="0"/>
+        <v>3003003</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F6" s="2">
+        <v>300</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7" s="2">
+        <f t="shared" si="0"/>
+        <v>3003004</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F7" s="2">
+        <v>400</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" s="2">
+        <f t="shared" si="0"/>
+        <v>3003005</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F8" s="2">
+        <v>500</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" s="2">
+        <f t="shared" si="0"/>
+        <v>3003006</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F9" s="2">
+        <v>600</v>
+      </c>
+      <c r="G9" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" s="2">
+        <f t="shared" si="0"/>
+        <v>3003007</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F10" s="2">
+        <v>700</v>
+      </c>
+      <c r="G10" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="2">
+        <f t="shared" si="0"/>
+        <v>3003008</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F11" s="2">
+        <v>800</v>
+      </c>
+      <c r="G11" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="2">
+        <f t="shared" si="0"/>
+        <v>3003009</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F12" s="2">
+        <v>900</v>
+      </c>
+      <c r="G12" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="2">
+        <f>(C13+1)*1000000+D13*1000+G13</f>
+        <v>3003010</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="2">
+        <f>(C14+1)*1000000+D14*1000+G14</f>
+        <v>3003011</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>100001</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1100</v>
+      </c>
+      <c r="G14" s="2">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F4" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F12" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="E2">
@@ -1334,11 +1547,11 @@
   <conditionalFormatting sqref="F3">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:C4">
+  <conditionalFormatting sqref="B1 B2:C2 B13:C13 B14 B15:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:C4 B5:B14">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C2 B5:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/task.xlsx
+++ b/data/config/luban/config/general/task.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="17100" windowHeight="7005"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1244,8 +1244,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
@@ -1255,7 +1255,7 @@
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1303,255 +1303,224 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:7">
+    <row r="4" s="2" customFormat="1" spans="1:6">
       <c r="B4" s="2">
-        <f t="shared" ref="B4:B13" si="0">(C4+1)*1000000+D4*1000+G4</f>
-        <v>3003001</v>
+        <v>300324001</v>
       </c>
       <c r="C4" s="2">
+        <f>IF(B4="","",MOD(INT(B4/100000000),10)-1)</f>
         <v>2</v>
       </c>
       <c r="D4" s="2">
+        <f>IF(B4="","",MOD(INT(B4/100000),10))</f>
         <v>3</v>
       </c>
       <c r="E4" s="2">
-        <v>100001</v>
+        <v>7024001</v>
       </c>
       <c r="F4" s="2">
-        <v>100</v>
-      </c>
-      <c r="G4" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="B5" s="2">
+        <v>300324002</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" ref="C5:C14" si="0">IF(B5="","",MOD(INT(B5/100000000),10)-1)</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" ref="D5:D14" si="1">IF(B5="","",MOD(INT(B5/100000),10))</f>
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7024002</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="2">
+        <v>300324003</v>
+      </c>
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
-        <v>3003002</v>
-      </c>
-      <c r="C5" s="2">
         <v>2</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D6" s="2">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E5" s="2">
-        <v>100001</v>
-      </c>
-      <c r="F5" s="2">
-        <v>200</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="E6" s="2">
+        <v>7024003</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="C7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="2">
+        <v>300334001</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
+      <c r="D8" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>7034001</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="B6" s="2">
+    <row r="9" spans="1:6">
+      <c r="B9" s="2">
+        <v>300334002</v>
+      </c>
+      <c r="C9" s="2">
         <f t="shared" si="0"/>
-        <v>3003003</v>
-      </c>
-      <c r="C6" s="2">
         <v>2</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D9" s="2">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E6" s="2">
-        <v>100001</v>
-      </c>
-      <c r="F6" s="2">
-        <v>300</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="E9" s="2">
+        <v>7034002</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="2">
+        <v>300334003</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
+      <c r="E10" s="2">
+        <v>7034003</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="B7" s="2">
+    <row r="11" spans="1:6">
+      <c r="C11" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>3003004</v>
-      </c>
-      <c r="C7" s="2">
+        <v/>
+      </c>
+      <c r="D11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="2">
+        <v>300344001</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D12" s="2">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E7" s="2">
-        <v>100001</v>
-      </c>
-      <c r="F7" s="2">
-        <v>400</v>
-      </c>
-      <c r="G7" s="2">
-        <v>4</v>
+      <c r="E12" s="2">
+        <v>7044001</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="B8" s="2">
+    <row r="13" spans="1:6">
+      <c r="B13" s="2">
+        <v>300344002</v>
+      </c>
+      <c r="C13" s="2">
         <f t="shared" si="0"/>
-        <v>3003005</v>
-      </c>
-      <c r="C8" s="2">
         <v>2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D13" s="2">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E8" s="2">
-        <v>100001</v>
-      </c>
-      <c r="F8" s="2">
-        <v>500</v>
-      </c>
-      <c r="G8" s="2">
-        <v>5</v>
+      <c r="E13" s="2">
+        <v>7044002</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="B9" s="2">
+    <row r="14" spans="1:6">
+      <c r="B14" s="2">
+        <v>300344003</v>
+      </c>
+      <c r="C14" s="2">
         <f t="shared" si="0"/>
-        <v>3003006</v>
-      </c>
-      <c r="C9" s="2">
         <v>2</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D14" s="2">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E9" s="2">
-        <v>100001</v>
-      </c>
-      <c r="F9" s="2">
-        <v>600</v>
-      </c>
-      <c r="G9" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" s="2">
-        <f t="shared" si="0"/>
-        <v>3003007</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>100001</v>
-      </c>
-      <c r="F10" s="2">
-        <v>700</v>
-      </c>
-      <c r="G10" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11" s="2">
-        <f t="shared" si="0"/>
-        <v>3003008</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2">
-        <v>100001</v>
-      </c>
-      <c r="F11" s="2">
-        <v>800</v>
-      </c>
-      <c r="G11" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="2">
-        <f t="shared" si="0"/>
-        <v>3003009</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2">
-        <v>3</v>
-      </c>
-      <c r="E12" s="2">
-        <v>100001</v>
-      </c>
-      <c r="F12" s="2">
-        <v>900</v>
-      </c>
-      <c r="G12" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13" s="2">
-        <f>(C13+1)*1000000+D13*1000+G13</f>
-        <v>3003010</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2">
-        <v>3</v>
-      </c>
-      <c r="E13" s="2">
-        <v>100001</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G13" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="2">
-        <f>(C14+1)*1000000+D14*1000+G14</f>
-        <v>3003011</v>
-      </c>
-      <c r="C14" s="2">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2">
-        <v>3</v>
-      </c>
       <c r="E14" s="2">
-        <v>100001</v>
+        <v>7044003</v>
       </c>
       <c r="F14" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G14" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F12" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F6" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="E2">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:B6">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:B10">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:B14">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="E8:E14">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1 B2:C2 B13:C13 B14 B15:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:C4 B5:B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  <conditionalFormatting sqref="B1 B2:C2 B7 B11 B15:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/task.xlsx
+++ b/data/config/luban/config/general/task.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1244,7 +1244,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
@@ -1494,33 +1494,150 @@
         <v>1</v>
       </c>
     </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="2">
+        <v>400311002</v>
+      </c>
+      <c r="C16" s="2">
+        <f>IF(B16="","",MOD(INT(B16/100000000),10)-1)</f>
+        <v>3</v>
+      </c>
+      <c r="D16" s="2">
+        <f>IF(B16="","",MOD(INT(B16/100000),10))</f>
+        <v>3</v>
+      </c>
+      <c r="E16" s="2">
+        <v>7024001</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="2">
+        <v>400311003</v>
+      </c>
+      <c r="C17" s="2">
+        <f>IF(B17="","",MOD(INT(B17/100000000),10)-1)</f>
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <f>IF(B17="","",MOD(INT(B17/100000),10))</f>
+        <v>3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>7024001</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="2">
+        <v>400311004</v>
+      </c>
+      <c r="C18" s="2">
+        <f>IF(B18="","",MOD(INT(B18/100000000),10)-1)</f>
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <f>IF(B18="","",MOD(INT(B18/100000),10))</f>
+        <v>3</v>
+      </c>
+      <c r="E18" s="2">
+        <v>7024001</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="2">
+        <v>400311005</v>
+      </c>
+      <c r="C19" s="2">
+        <f>IF(B19="","",MOD(INT(B19/100000000),10)-1)</f>
+        <v>3</v>
+      </c>
+      <c r="D19" s="2">
+        <f>IF(B19="","",MOD(INT(B19/100000),10))</f>
+        <v>3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>7024001</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="2">
+        <v>400311006</v>
+      </c>
+      <c r="C20" s="2">
+        <f>IF(B20="","",MOD(INT(B20/100000000),10)-1)</f>
+        <v>3</v>
+      </c>
+      <c r="D20" s="2">
+        <f>IF(B20="","",MOD(INT(B20/100000),10))</f>
+        <v>3</v>
+      </c>
+      <c r="E20" s="2">
+        <v>7024001</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2">
+        <v>400311007</v>
+      </c>
+      <c r="C21" s="2">
+        <f>IF(B21="","",MOD(INT(B21/100000000),10)-1)</f>
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <f>IF(B21="","",MOD(INT(B21/100000),10))</f>
+        <v>3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>7024001</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F6" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F14" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:B6">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:B10">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:B14">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12:B14">
+  <conditionalFormatting sqref="B16:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:E14">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1 B2:C2 B7 B11 B15:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+  <conditionalFormatting sqref="B1 B2:C2 B7 B11 B15:C15 B22:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/task.xlsx
+++ b/data/config/luban/config/general/task.xlsx
@@ -1244,7 +1244,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
@@ -1499,11 +1499,11 @@
         <v>400311002</v>
       </c>
       <c r="C16" s="2">
-        <f>IF(B16="","",MOD(INT(B16/100000000),10)-1)</f>
+        <f t="shared" ref="C16:C21" si="2">IF(B16="","",MOD(INT(B16/100000000),10)-1)</f>
         <v>3</v>
       </c>
       <c r="D16" s="2">
-        <f>IF(B16="","",MOD(INT(B16/100000),10))</f>
+        <f t="shared" ref="D16:D21" si="3">IF(B16="","",MOD(INT(B16/100000),10))</f>
         <v>3</v>
       </c>
       <c r="E16" s="2">
@@ -1518,11 +1518,11 @@
         <v>400311003</v>
       </c>
       <c r="C17" s="2">
-        <f>IF(B17="","",MOD(INT(B17/100000000),10)-1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="D17" s="2">
-        <f>IF(B17="","",MOD(INT(B17/100000),10))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E17" s="2">
@@ -1537,11 +1537,11 @@
         <v>400311004</v>
       </c>
       <c r="C18" s="2">
-        <f>IF(B18="","",MOD(INT(B18/100000000),10)-1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="D18" s="2">
-        <f>IF(B18="","",MOD(INT(B18/100000),10))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E18" s="2">
@@ -1556,11 +1556,11 @@
         <v>400311005</v>
       </c>
       <c r="C19" s="2">
-        <f>IF(B19="","",MOD(INT(B19/100000000),10)-1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="D19" s="2">
-        <f>IF(B19="","",MOD(INT(B19/100000),10))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E19" s="2">
@@ -1575,11 +1575,11 @@
         <v>400311006</v>
       </c>
       <c r="C20" s="2">
-        <f>IF(B20="","",MOD(INT(B20/100000000),10)-1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="D20" s="2">
-        <f>IF(B20="","",MOD(INT(B20/100000),10))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E20" s="2">
@@ -1594,11 +1594,11 @@
         <v>400311007</v>
       </c>
       <c r="C21" s="2">
-        <f>IF(B21="","",MOD(INT(B21/100000000),10)-1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <f>IF(B21="","",MOD(INT(B21/100000),10))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E21" s="2">
@@ -1606,6 +1606,202 @@
       </c>
       <c r="F21" s="2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="D22" s="2" t="str">
+        <f>IF(B22="","",MOD(INT(B22/100000),10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="2">
+        <v>500211001</v>
+      </c>
+      <c r="C23" s="2">
+        <f>IF(B23="","",MOD(INT(B23/100000000),10)-1)</f>
+        <v>4</v>
+      </c>
+      <c r="D23" s="2">
+        <f>IF(B23="","",MOD(INT(B23/100000),10))</f>
+        <v>2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F23" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="2">
+        <v>500211002</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" ref="C24:C31" si="4">IF(B24="","",MOD(INT(B24/100000000),10)-1)</f>
+        <v>4</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" ref="D24:D32" si="5">IF(B24="","",MOD(INT(B24/100000),10))</f>
+        <v>2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F24" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="2">
+        <v>500211003</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F25" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="2">
+        <v>500211004</v>
+      </c>
+      <c r="C26" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F26" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="2">
+        <v>500211005</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F27" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="2">
+        <v>500211006</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F28" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="2">
+        <v>500211007</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F29" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="2">
+        <v>500211008</v>
+      </c>
+      <c r="C30" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F30" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="2">
+        <v>500211009</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F31" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="2">
+        <v>500211010</v>
+      </c>
+      <c r="C32" s="2">
+        <f>IF(B32="","",MOD(INT(B32/100000000),10)-1)</f>
+        <v>4</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1010000</v>
+      </c>
+      <c r="F32" s="2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1613,31 +1809,34 @@
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:B6">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:B10">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:B14">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12:B14">
+  <conditionalFormatting sqref="B16:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B21">
+  <conditionalFormatting sqref="B23:B32">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:E14">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1 B2:C2 B7 B11 B15:C15 B22:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+  <conditionalFormatting sqref="B1 B2:C2 B7 B11 B15:C15 B22:C22 B33 B34:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
